--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340145</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340147</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339888</v>
       </c>
       <c r="B4" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340142</v>
       </c>
       <c r="B5" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340145</v>
+        <v>128339888</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>826600</v>
+        <v>826810</v>
       </c>
       <c r="R2" t="n">
-        <v>7397753</v>
+        <v>7397459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340147</v>
+        <v>128340143</v>
       </c>
       <c r="B3" t="n">
-        <v>92810</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>826696</v>
+        <v>826899</v>
       </c>
       <c r="R3" t="n">
-        <v>7397550</v>
+        <v>7397619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339888</v>
+        <v>128340142</v>
       </c>
       <c r="B4" t="n">
-        <v>92792</v>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>826810</v>
+        <v>826962</v>
       </c>
       <c r="R4" t="n">
-        <v>7397459</v>
+        <v>7397590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,14 +993,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340142</v>
+        <v>128340145</v>
       </c>
       <c r="B5" t="n">
-        <v>92810</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>826962</v>
+        <v>826600</v>
       </c>
       <c r="R5" t="n">
-        <v>7397590</v>
+        <v>7397753</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,11 +1102,11 @@
         <v>128340146</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1202,6 +1202,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128340147</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Naisjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>826696</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7397550</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42872-2025 artfynd.xlsx
+++ b/artfynd/A 42872-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340143</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340142</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340145</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>